--- a/artfynd/A 25171-2026 artfynd.xlsx
+++ b/artfynd/A 25171-2026 artfynd.xlsx
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66510142</v>
+        <v>117906161</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Mpd</t>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602491.0047327239</v>
+        <v>602589</v>
       </c>
       <c r="R2" t="n">
-        <v>6964079.970048527</v>
+        <v>6963986</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +760,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66510146</v>
+        <v>66510142</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602509.9002529512</v>
+        <v>602491</v>
       </c>
       <c r="R3" t="n">
-        <v>6964076.896649277</v>
+        <v>6964080</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +844,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -891,7 +860,7 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66510143</v>
+        <v>117906160</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +889,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Mpd</t>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602491.0047327239</v>
+        <v>602513</v>
       </c>
       <c r="R4" t="n">
-        <v>6964079.970048527</v>
+        <v>6964130</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,36 +963,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>18875</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66510151</v>
+        <v>66510148</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1042,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602445.5166338766</v>
+        <v>602466</v>
       </c>
       <c r="R5" t="n">
-        <v>6964127.086062239</v>
+        <v>6964037</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1099,21 +1047,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1125,7 +1063,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>18883</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1143,37 +1081,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66510147</v>
+        <v>66510144</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1116,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602465.7631450084</v>
+        <v>602491</v>
       </c>
       <c r="R6" t="n">
-        <v>6964036.599263771</v>
+        <v>6964080</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1216,21 +1149,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1242,7 +1165,7 @@
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1260,37 +1183,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66510144</v>
+        <v>66510138</v>
       </c>
       <c r="B7" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1300,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602491.0047327239</v>
+        <v>602511</v>
       </c>
       <c r="R7" t="n">
-        <v>6964079.970048527</v>
+        <v>6964240</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1333,21 +1251,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1359,7 +1267,7 @@
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>18876</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1377,19 +1285,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66510152</v>
+        <v>66510141</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1417,10 +1320,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602445.5166338766</v>
+        <v>602507</v>
       </c>
       <c r="R8" t="n">
-        <v>6964127.086062239</v>
+        <v>6964130</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1450,21 +1353,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1476,7 +1369,7 @@
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1494,37 +1387,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66510149</v>
+        <v>66510143</v>
       </c>
       <c r="B9" t="n">
-        <v>77756</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1422,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602465.7631450084</v>
+        <v>602491</v>
       </c>
       <c r="R9" t="n">
-        <v>6964036.599263771</v>
+        <v>6964080</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1567,21 +1455,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1593,7 +1471,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>18881</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1611,37 +1489,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66510148</v>
+        <v>66510146</v>
       </c>
       <c r="B10" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1524,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602465.7631450084</v>
+        <v>602510</v>
       </c>
       <c r="R10" t="n">
-        <v>6964036.599263771</v>
+        <v>6964077</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1684,21 +1557,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1710,7 +1573,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1731,16 +1594,11 @@
         <v>66510150</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1768,10 +1626,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602465.7631450084</v>
+        <v>602466</v>
       </c>
       <c r="R11" t="n">
-        <v>6964036.599263771</v>
+        <v>6964037</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1801,19 +1659,9 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1845,54 +1693,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66510140</v>
+        <v>66510152</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602507.3280807361</v>
+        <v>602446</v>
       </c>
       <c r="R12" t="n">
-        <v>6964129.930295645</v>
+        <v>6964127</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1922,21 +1761,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1948,7 +1777,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1969,12 +1798,7 @@
         <v>66510139</v>
       </c>
       <c r="B13" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2006,10 +1830,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>602507.4913151695</v>
+        <v>602507</v>
       </c>
       <c r="R13" t="n">
-        <v>6964198.158051495</v>
+        <v>6964198</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -2039,19 +1863,9 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2013-09-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,37 +1897,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66510138</v>
+        <v>66510154</v>
       </c>
       <c r="B14" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2123,10 +1932,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602511.2308520913</v>
+        <v>602450</v>
       </c>
       <c r="R14" t="n">
-        <v>6964239.940261365</v>
+        <v>6964292</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2156,21 +1965,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2182,7 +1981,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>18870</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2200,50 +1999,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66510154</v>
+        <v>66510140</v>
       </c>
       <c r="B15" t="n">
-        <v>78503</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602450.457644333</v>
+        <v>602507</v>
       </c>
       <c r="R15" t="n">
-        <v>6964292.070973505</v>
+        <v>6964130</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2273,21 +2071,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2299,7 +2087,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2317,15 +2105,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66510141</v>
+        <v>66510145</v>
       </c>
       <c r="B16" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2333,21 +2116,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2357,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602507.3280807361</v>
+        <v>602510</v>
       </c>
       <c r="R16" t="n">
-        <v>6964129.930295645</v>
+        <v>6964077</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2390,21 +2173,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2416,7 +2189,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>18873</t>
+          <t>18877</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2434,15 +2207,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66510145</v>
+        <v>66510147</v>
       </c>
       <c r="B17" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2474,10 +2242,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602509.9002529512</v>
+        <v>602466</v>
       </c>
       <c r="R17" t="n">
-        <v>6964076.896649277</v>
+        <v>6964037</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2507,21 +2275,11 @@
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2013-09-24</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2533,7 +2291,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18879</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2551,57 +2309,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117906158</v>
+        <v>66510151</v>
       </c>
       <c r="B18" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602480</v>
+        <v>602446</v>
       </c>
       <c r="R18" t="n">
-        <v>6964194</v>
+        <v>6964127</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2625,12 +2374,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2013-09-24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2013-09-24</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2641,53 +2390,53 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>18883</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117906161</v>
+        <v>117906156</v>
       </c>
       <c r="B19" t="n">
-        <v>94352</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2701,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602589</v>
+        <v>602464</v>
       </c>
       <c r="R19" t="n">
-        <v>6963986</v>
+        <v>6964278</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2763,57 +2512,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117906163</v>
+        <v>66510149</v>
       </c>
       <c r="B20" t="n">
-        <v>97840</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6459</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602515</v>
+        <v>602466</v>
       </c>
       <c r="R20" t="n">
-        <v>6964021</v>
+        <v>6964037</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2837,12 +2577,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2013-09-24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2013-09-24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2853,58 +2593,58 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>18881</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117906156</v>
+        <v>117906158</v>
       </c>
       <c r="B21" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2913,13 +2653,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602464</v>
+        <v>602480</v>
       </c>
       <c r="R21" t="n">
-        <v>6964278</v>
+        <v>6964194</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2975,42 +2715,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117906160</v>
+        <v>117906163</v>
       </c>
       <c r="B22" t="n">
-        <v>90503</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3019,10 +2754,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602513</v>
+        <v>602515</v>
       </c>
       <c r="R22" t="n">
-        <v>6964130</v>
+        <v>6964021</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 25171-2026 artfynd.xlsx
+++ b/artfynd/A 25171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117906161</v>
+        <v>134787082</v>
       </c>
       <c r="B2" t="n">
-        <v>96446</v>
+        <v>83350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1079</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602589</v>
+        <v>602427</v>
       </c>
       <c r="R2" t="n">
-        <v>6963986</v>
+        <v>6964252</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,12 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66510142</v>
+        <v>134787085</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>89354</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602491</v>
+        <v>602449</v>
       </c>
       <c r="R3" t="n">
-        <v>6964080</v>
+        <v>6964257</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -841,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,53 +873,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117906160</v>
+        <v>117906161</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>96446</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -917,13 +928,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>602513</v>
+        <v>602589</v>
       </c>
       <c r="R4" t="n">
-        <v>6964130</v>
+        <v>6963986</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,10 +990,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66510148</v>
+        <v>66510142</v>
       </c>
       <c r="B5" t="n">
-        <v>80433</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -990,21 +1001,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1014,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>602466</v>
+        <v>602491</v>
       </c>
       <c r="R5" t="n">
-        <v>6964037</v>
+        <v>6964080</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1063,7 +1074,7 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1081,48 +1092,52 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66510144</v>
+        <v>117906160</v>
       </c>
       <c r="B6" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomtjärnen, Mpd</t>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602491</v>
+        <v>602513</v>
       </c>
       <c r="R6" t="n">
-        <v>6964080</v>
+        <v>6964130</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1146,12 +1161,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2024-06-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1162,53 +1177,48 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>18876</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66510138</v>
+        <v>134787091</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>91974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1218,13 +1228,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602511</v>
+        <v>602398</v>
       </c>
       <c r="R7" t="n">
-        <v>6964240</v>
+        <v>6964192</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1248,12 +1258,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1264,53 +1284,48 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>18870</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66510141</v>
+        <v>134787092</v>
       </c>
       <c r="B8" t="n">
-        <v>79327</v>
+        <v>91974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1320,13 +1335,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>602507</v>
+        <v>602402</v>
       </c>
       <c r="R8" t="n">
-        <v>6964130</v>
+        <v>6964193</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1350,12 +1365,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1366,53 +1391,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>18873</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66510143</v>
+        <v>66510148</v>
       </c>
       <c r="B9" t="n">
-        <v>79327</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1422,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>602491</v>
+        <v>602466</v>
       </c>
       <c r="R9" t="n">
-        <v>6964080</v>
+        <v>6964037</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1471,7 +1491,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>18875</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1489,32 +1509,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66510146</v>
+        <v>66510144</v>
       </c>
       <c r="B10" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1524,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>602510</v>
+        <v>602491</v>
       </c>
       <c r="R10" t="n">
-        <v>6964077</v>
+        <v>6964080</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1573,7 +1593,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>18878</t>
+          <t>18876</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1591,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66510150</v>
+        <v>134787088</v>
       </c>
       <c r="B11" t="n">
-        <v>79327</v>
+        <v>91937</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1626,13 +1646,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>602466</v>
+        <v>602425</v>
       </c>
       <c r="R11" t="n">
-        <v>6964037</v>
+        <v>6964211</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1656,12 +1676,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,28 +1702,23 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>18882</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66510152</v>
+        <v>66510138</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1728,10 +1753,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>602446</v>
+        <v>602511</v>
       </c>
       <c r="R12" t="n">
-        <v>6964127</v>
+        <v>6964240</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1777,7 +1802,7 @@
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>18884</t>
+          <t>18870</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1795,32 +1820,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>66510139</v>
+        <v>66510141</v>
       </c>
       <c r="B13" t="n">
-        <v>83290</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1833,7 +1858,7 @@
         <v>602507</v>
       </c>
       <c r="R13" t="n">
-        <v>6964198</v>
+        <v>6964130</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1879,7 +1904,7 @@
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18873</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1897,32 +1922,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>66510154</v>
+        <v>66510143</v>
       </c>
       <c r="B14" t="n">
-        <v>80336</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1932,10 +1957,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>602450</v>
+        <v>602491</v>
       </c>
       <c r="R14" t="n">
-        <v>6964292</v>
+        <v>6964080</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -1981,7 +2006,7 @@
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18875</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -1999,49 +2024,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>66510140</v>
+        <v>66510146</v>
       </c>
       <c r="B15" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>602507</v>
+        <v>602510</v>
       </c>
       <c r="R15" t="n">
-        <v>6964130</v>
+        <v>6964077</v>
       </c>
       <c r="S15" t="n">
         <v>50</v>
@@ -2087,7 +2108,7 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>18878</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2105,32 +2126,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>66510145</v>
+        <v>66510150</v>
       </c>
       <c r="B16" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2140,10 +2161,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>602510</v>
+        <v>602466</v>
       </c>
       <c r="R16" t="n">
-        <v>6964077</v>
+        <v>6964037</v>
       </c>
       <c r="S16" t="n">
         <v>50</v>
@@ -2189,7 +2210,7 @@
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>18877</t>
+          <t>18882</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2207,32 +2228,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>66510147</v>
+        <v>66510152</v>
       </c>
       <c r="B17" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2242,10 +2263,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>602466</v>
+        <v>602446</v>
       </c>
       <c r="R17" t="n">
-        <v>6964037</v>
+        <v>6964127</v>
       </c>
       <c r="S17" t="n">
         <v>50</v>
@@ -2291,7 +2312,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>18879</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2309,32 +2330,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>66510151</v>
+        <v>134787080</v>
       </c>
       <c r="B18" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2344,13 +2365,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>602446</v>
+        <v>602381</v>
       </c>
       <c r="R18" t="n">
-        <v>6964127</v>
+        <v>6964231</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2374,12 +2395,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2390,73 +2421,64 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>18883</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117906156</v>
+        <v>134787083</v>
       </c>
       <c r="B19" t="n">
-        <v>80432</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>602464</v>
+        <v>602427</v>
       </c>
       <c r="R19" t="n">
-        <v>6964278</v>
+        <v>6964254</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2480,12 +2502,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2500,44 +2532,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>66510149</v>
+        <v>134787095</v>
       </c>
       <c r="B20" t="n">
-        <v>79583</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2547,13 +2579,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>602466</v>
+        <v>602411</v>
       </c>
       <c r="R20" t="n">
-        <v>6964037</v>
+        <v>6964199</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2577,12 +2609,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2013-09-24</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2593,31 +2635,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>18881</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117906158</v>
+        <v>134787099</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2625,38 +2662,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>602480</v>
+        <v>602363</v>
       </c>
       <c r="R21" t="n">
-        <v>6964194</v>
+        <v>6964193</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2683,12 +2716,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2703,22 +2746,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Maria Edstam</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117906163</v>
+        <v>134787102</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,38 +2769,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+          <t>Lomtjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>602515</v>
+        <v>602316</v>
       </c>
       <c r="R22" t="n">
-        <v>6964021</v>
+        <v>6964195</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2784,12 +2823,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-15</t>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2804,15 +2853,3270 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>66510139</v>
+      </c>
+      <c r="B23" t="n">
+        <v>83290</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>602507</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6964198</v>
+      </c>
+      <c r="S23" t="n">
+        <v>50</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>18871</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>66510154</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>602450</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6964292</v>
+      </c>
+      <c r="S24" t="n">
+        <v>50</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>18885</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>66510140</v>
+      </c>
+      <c r="B25" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>602507</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6964130</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>18872</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>66510145</v>
+      </c>
+      <c r="B26" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>602510</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6964077</v>
+      </c>
+      <c r="S26" t="n">
+        <v>50</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>18877</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>66510147</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>602466</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6964037</v>
+      </c>
+      <c r="S27" t="n">
+        <v>50</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>18879</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>66510151</v>
+      </c>
+      <c r="B28" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>602446</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6964127</v>
+      </c>
+      <c r="S28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>18883</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>117906156</v>
+      </c>
+      <c r="B29" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>602464</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6964278</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX29" t="inlineStr">
         <is>
           <t>Maria Edstam</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>66510149</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79583</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>602466</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6964037</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2013-09-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>18881</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Via Malin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>134787097</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>602398</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6964211</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>15:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>134787081</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>602430</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6964248</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>134787084</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>602420</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6964274</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>134787086</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>602471</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6964249</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>134787087</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>602426</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6964230</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>134787089</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>pulli/nyligen flygga ungar</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>602404</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6964172</v>
+      </c>
+      <c r="S36" t="n">
+        <v>6</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>En tretå-unge som nyligen lämnat boet observeras. Ungen sitter tryckt mot trädstammen och verkar hoppas att den inte syns.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>134787090</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>602400</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6964172</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134787094</v>
+      </c>
+      <c r="B38" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>602406</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6964197</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134787098</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>602376</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6964195</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134787104</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>602342</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6964214</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Tretå-hane gör ringhack på tall. Observationen gjordes med kikare från drygt 10 meters håll.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134787105</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>602328</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6964214</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134787108</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>602433</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6964193</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134787109</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>602464</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6964196</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:19</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134787111</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>602475</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6964153</v>
+      </c>
+      <c r="S44" t="n">
+        <v>6</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på nedfallen tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>117906158</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>602480</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6964194</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>117906163</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SkÃ¤lgÃ¥rden, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>602515</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6964021</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-06-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Maria Edstam</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134787100</v>
+      </c>
+      <c r="B47" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>602353</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6964189</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>15:54</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>90 ex</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134787103</v>
+      </c>
+      <c r="B48" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>602342</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6964202</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>10 ex</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134787106</v>
+      </c>
+      <c r="B49" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>602333</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6964188</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>120 ex</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134787107</v>
+      </c>
+      <c r="B50" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>602424</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6964182</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>50 ex</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134787101</v>
+      </c>
+      <c r="B51" t="n">
+        <v>98066</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lomtjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>602307</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6964183</v>
+      </c>
+      <c r="S51" t="n">
+        <v>5</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:59</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25171-2026 artfynd.xlsx
+++ b/artfynd/A 25171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY51"/>
+  <dimension ref="A1:AZ51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787092</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787080</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787095</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787099</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787102</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787097</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787084</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787087</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1892,6 +1947,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787089</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787090</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2132,6 +2197,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787094</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2252,6 +2322,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787098</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2380,6 +2455,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787104</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2500,6 +2580,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787105</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2612,6 +2697,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787100</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2724,6 +2814,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787103</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2836,6 +2931,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787106</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2948,6 +3048,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787107</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3055,6 +3160,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787101</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3162,6 +3272,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787082</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3269,6 +3384,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787085</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3370,6 +3490,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906161</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3472,6 +3597,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510142</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3573,6 +3703,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906160</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3675,6 +3810,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510148</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3777,6 +3917,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510144</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3879,6 +4024,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510138</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3981,6 +4131,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510141</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4083,6 +4238,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510143</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4185,6 +4345,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510146</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4287,6 +4452,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510150</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4389,6 +4559,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510152</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4496,6 +4671,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787083</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4598,6 +4778,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510139</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4700,6 +4885,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510154</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4806,6 +4996,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510140</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4908,6 +5103,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510145</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5010,6 +5210,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510147</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5112,6 +5317,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510151</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5213,6 +5423,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906156</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5315,6 +5530,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66510149</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5435,6 +5655,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787081</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5555,6 +5780,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787086</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5675,6 +5905,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787108</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5795,6 +6030,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787109</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5915,6 +6155,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134787111</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6016,6 +6261,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906158</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6117,8 +6367,65 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117906163</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>